--- a/test-cases/output/finalunder_doc.xlsx
+++ b/test-cases/output/finalunder_doc.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,10 +33,16 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,17 +56,41 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="002E74B5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001F3864"/>
+      </left>
+      <right style="medium">
+        <color rgb="001F3864"/>
+      </right>
+      <top style="medium">
+        <color rgb="001F3864"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001F3864"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -80,13 +110,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -453,23 +489,370 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>final_understanding_document</t>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>{"document_overview": "This consolidated document presents a unified understanding of an Agentic AI-driven Quality Engineering (QE) pipeline. It describes the transition from traditional script-based automation to autonomous, multi-agent AI frameworks that manage the entire testing lifecycle. The pipeline covers requirements ingestion, scenario generation, test case authoring, publishing, and integration with test management tools. The approach emphasizes modular agent roles, traceability, automation, and user-centric design, with insights from architecture, workflow, business, and UI/UX perspectives.", "technical_understanding": ["Agentic AI enables autonomous planning, reasoning, and execution of QE tasks, reducing manual intervention and increasing efficiency.", "The pipeline is composed of specialized agents (Ingestion, Planner, Authoring, Publisher), each responsible for distinct phases of the test lifecycle.", "Integration with project management (e.g., Jira) and test management systems (e.g., TestRail) is achieved via secure APIs.", "Large Language Models (LLMs) are leveraged for scenario deduction and test case generation.", "Strict schema and standardized JSON formats ensure compatibility and traceability."], "business_understanding": ["The primary business goal is to automate test case generation, ensuring traceability and compliance while accelerating QA cycles.", "Manual translation of requirements to test cases is eliminated, reducing errors and increasing coverage.", "Every generated test step maps directly to business requirements, supporting auditability and regulatory needs.", "The approach supports scalable, efficient, and compliant QA processes, with clear division of agent responsibilities."], "workflow_understanding": ["User story is flagged as Ready for QA in the issue tracking system.", "Ingestion Agent extracts and cleanses all relevant user story fields via API.", "Planner Agent generates a test coverage matrix, categorizing scenarios (happy path, error handling, boundary values, security/access).", "Authoring Agent translates scenarios into detailed test steps, pre-conditions, and expected results.", "Publisher Agent formats and publishes test cases to the test management system, ensuring traceability."], "architecture_understanding": ["The pipeline is modular, with each agent handling a specific phase: Ingestion &amp; Parsing, Scenario Planning, Test Authoring, and Publishing.", "Agents communicate sequentially, transforming and enriching data at each stage.", "API-driven integration ensures seamless data flow between enterprise systems.", "Traceability is maintained by mapping test steps to original business requirements."], "ui_ux_understanding": ["UI/UX design (from Figma) emphasizes clarity, ease of navigation, and efficient workflow for cart management and checkout in an e-commerce context.", "User flows are linear and intuitive, with real-time feedback for actions like quantity adjustments and item removal.", "Component usage is consistent, with prominent action buttons, clear order summaries, and persistent navigation elements.", "Design gaps identified include lack of error handling UI, missing validation for max quantity, and absence of guest checkout options."], "important_observations": ["Absolute traceability is achieved by mapping test steps to business requirements.", "Manual data entry is eliminated, reducing errors and increasing speed.", "Coverage matrix ensures comprehensive testing across all scenario categories.", "The modular agent approach supports scalability and maintainability.", "Some limitations exist in extracting insights from image-based content due to tool constraints."], "final_conclusion": "Agentic AI-powered QE pipelines represent a paradigm shift in quality engineering, automating the entire test lifecycle from requirements analysis to test case authoring and publishing. By leveraging autonomous agents, LLMs, and robust integrations, organizations can achieve higher efficiency, better coverage, and improved traceability. The approach is further strengthened by user-centric UI/UX design, though there are opportunities for enhancement in error handling and validation. Overall, this unified framework sets a new standard for scalable, automated, and business-aligned quality engineering."}</t>
+          <t>Document Overview</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>This consolidated document presents a unified understanding of an Agentic AI-driven Quality Engineering (QE) pipeline. It describes the transition from traditional script-based automation to autonomous, multi-agent AI frameworks that manage the entire testing lifecycle. The pipeline covers requirements ingestion, scenario generation, test case authoring, publishing, and integration with test management tools. The approach emphasizes modular agent roles, traceability, automation, and user-centric design, with insights from architecture, workflow, business, and UI/UX perspectives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Technical Understanding</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Agentic AI enables autonomous planning, reasoning, and execution of QE tasks, reducing manual intervention and increasing efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Technical Understanding</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>The pipeline is composed of specialized agents (Ingestion, Planner, Authoring, Publisher), each responsible for distinct phases of the test lifecycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Technical Understanding</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Integration with project management (e.g., Jira) and test management systems (e.g., TestRail) is achieved via secure APIs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Technical Understanding</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Large Language Models (LLMs) are leveraged for scenario deduction and test case generation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Technical Understanding</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Strict schema and standardized JSON formats ensure compatibility and traceability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Business Understanding</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>The primary business goal is to automate test case generation, ensuring traceability and compliance while accelerating QA cycles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Business Understanding</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Manual translation of requirements to test cases is eliminated, reducing errors and increasing coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Business Understanding</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Every generated test step maps directly to business requirements, supporting auditability and regulatory needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Business Understanding</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>The approach supports scalable, efficient, and compliant QA processes, with clear division of agent responsibilities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Workflow Understanding</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>User story is flagged as Ready for QA in the issue tracking system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Workflow Understanding</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Ingestion Agent extracts and cleanses all relevant user story fields via API.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Workflow Understanding</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Planner Agent generates a test coverage matrix, categorizing scenarios (happy path, error handling, boundary values, security/access).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Workflow Understanding</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Authoring Agent translates scenarios into detailed test steps, pre-conditions, and expected results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Workflow Understanding</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Publisher Agent formats and publishes test cases to the test management system, ensuring traceability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Architecture Understanding</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>The pipeline is modular, with each agent handling a specific phase: Ingestion &amp; Parsing, Scenario Planning, Test Authoring, and Publishing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Architecture Understanding</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Agents communicate sequentially, transforming and enriching data at each stage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Architecture Understanding</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>API-driven integration ensures seamless data flow between enterprise systems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Architecture Understanding</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Traceability is maintained by mapping test steps to original business requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Ui Ux Understanding</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>UI/UX design (from Figma) emphasizes clarity, ease of navigation, and efficient workflow for cart management and checkout in an e-commerce context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Ui Ux Understanding</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>User flows are linear and intuitive, with real-time feedback for actions like quantity adjustments and item removal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Ui Ux Understanding</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Component usage is consistent, with prominent action buttons, clear order summaries, and persistent navigation elements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Ui Ux Understanding</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Design gaps identified include lack of error handling UI, missing validation for max quantity, and absence of guest checkout options.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Important Observations</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Absolute traceability is achieved by mapping test steps to business requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Important Observations</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Manual data entry is eliminated, reducing errors and increasing speed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Important Observations</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Coverage matrix ensures comprehensive testing across all scenario categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Important Observations</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>The modular agent approach supports scalability and maintainability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Important Observations</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Some limitations exist in extracting insights from image-based content due to tool constraints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Final Conclusion</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Agentic AI-powered QE pipelines represent a paradigm shift in quality engineering, automating the entire test lifecycle from requirements analysis to test case authoring and publishing. By leveraging autonomous agents, LLMs, and robust integrations, organizations can achieve higher efficiency, better coverage, and improved traceability. The approach is further strengthened by user-centric UI/UX design, though there are opportunities for enhancement in error handling and validation. Overall, this unified framework sets a new standard for scalable, automated, and business-aligned quality engineering.</t>
         </is>
       </c>
     </row>
